--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46256.44070865515</v>
+        <v>46256.56483071856</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46256.56483071856</v>
+        <v>46256.73145981103</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46256.73145981103</v>
+        <v>46257.440122557</v>
       </c>
     </row>
     <row r="4">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>223429</v>
+        <v>223365</v>
       </c>
     </row>
     <row r="21">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46257.440122557</v>
+        <v>46257.56555753975</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46258.87340095438</v>
+        <v>46258.9011162666</v>
       </c>
     </row>
     <row r="4">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>305</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46260.83392806401</v>
+        <v>46260.85811937377</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46269.77739757375</v>
+        <v>46270.4458222071</v>
       </c>
     </row>
     <row r="4">
@@ -993,7 +993,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C - %61.9 (n=1278); E - %61.0 (n=1326); F - %60.7 (n=1077); K - %60.9 (n=1349); L - %61.0 (n=1035)</t>
+          <t>C - %61.9 (n=1280); E - %61.0 (n=1328); F - %60.7 (n=1077); K - %60.8 (n=1351); L - %61.0 (n=1035)</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); D - %67.8 (n=320); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); D - %67.8 (n=320); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C - %61.9 (n=1278); E - %61.0 (n=1326); F - %60.7 (n=1077); K - %60.9 (n=1349); L - %61.0 (n=1035)</t>
+          <t>C - %61.9 (n=1280); E - %61.0 (n=1328); F - %60.7 (n=1077); K - %60.8 (n=1351); L - %61.0 (n=1035)</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>C - %61.9 (n=1278); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>C - %61.9 (n=1280); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); D - %67.8 (n=320); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); D - %67.8 (n=320); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); G - %68.7 (n=214); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); G - %68.3 (n=218); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); G - %68.7 (n=214); K - %66.6 (n=533)</t>
+          <t>C - %69.2 (n=386); G - %68.3 (n=218); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); D - %67.8 (n=320); J - %72.1 (n=365); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>C - %69.2 (n=386); D - %67.8 (n=320); J - %71.7 (n=375); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>C - %69.2 (n=386); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); F - %68.6 (n=159); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); F - %68.6 (n=159); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); G - %68.7 (n=214); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); G - %68.3 (n=218); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); E - %69.8 (n=202); G - %68.7 (n=214); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); E - %69.6 (n=207); G - %68.3 (n=218); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); E - %69.8 (n=202); G - %68.7 (n=214); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); E - %69.6 (n=207); G - %68.3 (n=218); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); G - %68.7 (n=214); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); G - %68.3 (n=218); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533); L - %66.7 (n=363)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552); L - %66.8 (n=364)</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); H - %69.4 (n=206); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); H - %68.2 (n=211); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); C - %61.9 (n=1278); E - %61.0 (n=1326); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); C - %61.9 (n=1280); E - %61.0 (n=1328); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); C - %61.9 (n=1278); E - %61.0 (n=1326); G - %60.3 (n=489); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); C - %61.9 (n=1280); E - %61.0 (n=1328); G - %60.2 (n=490); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); E - %69.8 (n=202); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); E - %69.6 (n=207); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); C - %70.3 (n=367); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); C - %69.2 (n=386); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); E - %61.0 (n=1326); F - %60.7 (n=1077); K - %60.9 (n=1349); L - %61.0 (n=1035)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); E - %61.0 (n=1328); F - %60.7 (n=1077); K - %60.8 (n=1351); L - %61.0 (n=1035)</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); F - %60.7 (n=1077); K - %60.9 (n=1349); L - %61.0 (n=1035)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); F - %60.7 (n=1077); K - %60.8 (n=1351); L - %61.0 (n=1035)</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); E - %61.0 (n=1326); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); E - %61.0 (n=1328); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); E - %61.0 (n=1326); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); E - %61.0 (n=1328); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); E - %61.0 (n=1326); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); E - %61.0 (n=1328); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); E - %61.0 (n=1326); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); E - %61.0 (n=1328); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>A - %69.4 (n=242); B - %77.3 (n=238); C - %70.3 (n=367); H - %69.4 (n=206); I - %72.5 (n=255); J - %72.1 (n=365); K - %66.6 (n=533)</t>
+          <t>A - %67.8 (n=261); B - %75.8 (n=248); C - %69.2 (n=386); H - %68.2 (n=211); I - %71.8 (n=259); J - %71.7 (n=375); K - %65.9 (n=552)</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); B - %66.1 (n=694); C - %61.9 (n=1278); H - %63.6 (n=338); K - %60.9 (n=1349)</t>
+          <t>A - %63.4 (n=849); B - %66.1 (n=694); C - %61.9 (n=1280); H - %63.6 (n=338); K - %60.8 (n=1351)</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>A - %63.4 (n=847); C - %61.9 (n=1278); E - %61.0 (n=1326); F - %60.7 (n=1077); K - %60.9 (n=1349); L - %61.0 (n=1035)</t>
+          <t>A - %63.4 (n=849); C - %61.9 (n=1280); E - %61.0 (n=1328); F - %60.7 (n=1077); K - %60.8 (n=1351); L - %61.0 (n=1035)</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -6897,13 +6897,13 @@
         <v>46269</v>
       </c>
       <c r="G2" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="H2" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.6942148760330579</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -6937,13 +6937,13 @@
         <v>46269</v>
       </c>
       <c r="G3" t="n">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="H3" t="n">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.6340023612750886</v>
+        <v>0.6336866902237926</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -6977,13 +6977,13 @@
         <v>46269</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="H4" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.773109243697479</v>
+        <v>0.7580645161290323</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -7057,13 +7057,13 @@
         <v>46269</v>
       </c>
       <c r="G6" t="n">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="H6" t="n">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7029972752043597</v>
+        <v>0.6917098445595855</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -7097,13 +7097,13 @@
         <v>46269</v>
       </c>
       <c r="G7" t="n">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="H7" t="n">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.6189358372456965</v>
+        <v>0.61875</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -7217,13 +7217,13 @@
         <v>46269</v>
       </c>
       <c r="G10" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H10" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.698019801980198</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -7257,13 +7257,13 @@
         <v>46269</v>
       </c>
       <c r="G11" t="n">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="H11" t="n">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.610105580693816</v>
+        <v>0.6099397590361446</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -7377,13 +7377,13 @@
         <v>46269</v>
       </c>
       <c r="G14" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6869158878504673</v>
+        <v>0.6834862385321101</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -7417,13 +7417,13 @@
         <v>46269</v>
       </c>
       <c r="G15" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H15" t="n">
         <v>295</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6032719836400818</v>
+        <v>0.6020408163265306</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -7457,13 +7457,13 @@
         <v>46269</v>
       </c>
       <c r="G16" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="H16" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.6941747572815534</v>
+        <v>0.6824644549763034</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -7537,13 +7537,13 @@
         <v>46269</v>
       </c>
       <c r="G18" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H18" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7254901960784313</v>
+        <v>0.7181467181467182</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -7617,13 +7617,13 @@
         <v>46269</v>
       </c>
       <c r="G20" t="n">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H20" t="n">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.7205479452054795</v>
+        <v>0.7173333333333334</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -7697,13 +7697,13 @@
         <v>46269</v>
       </c>
       <c r="G22" t="n">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="H22" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.6660412757973734</v>
+        <v>0.6594202898550725</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         <v>46269</v>
       </c>
       <c r="G23" t="n">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="H23" t="n">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.6085989621942179</v>
+        <v>0.6084381939304219</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -7777,13 +7777,13 @@
         <v>46269</v>
       </c>
       <c r="G24" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H24" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6675824175824175</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PR_v3</t>
+          <t>PR_v4</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46270.4458222071</v>
+        <v>46271.71631938649</v>
       </c>
     </row>
     <row r="4">
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>223789</v>
+        <v>223725</v>
       </c>
     </row>
     <row r="21">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46271.71631938649</v>
+        <v>46271.76804117942</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46271.76804117942</v>
+        <v>46271.83538173488</v>
       </c>
     </row>
     <row r="4">

--- a/CNDL_tr.xlsx
+++ b/CNDL_tr.xlsx
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46276.62332608993</v>
+        <v>46276.78764146396</v>
       </c>
     </row>
     <row r="4">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="24">
@@ -793,7 +793,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
     <col width="42" customWidth="1" min="13" max="13"/>
@@ -967,83 +967,83 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11.36</v>
+        <v>294</v>
       </c>
       <c r="H2" t="n">
-        <v>11.36</v>
+        <v>294</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>B - %76.2 (n=260); C - %70.3 (n=404); D - %68.8 (n=330); H - %69.2 (n=224); I - %72.0 (n=261); J - %72.6 (n=387); K - %67.1 (n=563)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>-1.645023262982315</v>
+        <v>-2.244389027431426</v>
       </c>
       <c r="K2" t="n">
-        <v>5.674418604651166</v>
+        <v>-0.3389830508474523</v>
       </c>
       <c r="L2" t="n">
-        <v>3.085295152519429</v>
+        <v>-15.81961345740873</v>
       </c>
       <c r="M2" t="n">
-        <v>4284</v>
+        <v>649</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>0.5485527544351074</v>
+        <v>0.662557781201849</v>
       </c>
       <c r="O2" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="P2" s="4" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.53125</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>4282</v>
+        <v>649</v>
       </c>
       <c r="V2" s="4" t="n">
-        <v>0.6529659037832788</v>
+        <v>0.7596302003081664</v>
       </c>
       <c r="W2" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="X2" s="4" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="Z2" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6875</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1080,24 +1080,24 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>704</v>
+        <v>3.91000009</v>
       </c>
       <c r="H3" t="n">
-        <v>704</v>
+        <v>3.91000009</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); D - %65.6 (n=218); G - %60.9 (n=470); H - %63.3 (n=338); K - %61.1 (n=1312)</t>
+          <t>C - %62.2 (n=1250); D - %65.6 (n=218); F - %61.1 (n=1052); I - %69.9 (n=83); J - %72.4 (n=58); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>-3.363074811256006</v>
+        <v>5.107528453433918</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.607267645003496</v>
+        <v>2.356025174063303</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.097040605643497</v>
+        <v>-13.87664924120396</v>
       </c>
       <c r="M3" t="n">
         <v>4284</v>
@@ -1106,10 +1106,10 @@
         <v>0.5485527544351074</v>
       </c>
       <c r="O3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="P3" s="4" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="Q3" t="n">
         <v>93</v>
@@ -1130,10 +1130,10 @@
         <v>0.6529659037832788</v>
       </c>
       <c r="W3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="X3" s="4" t="n">
-        <v>0.5857142857142857</v>
+        <v>0.6</v>
       </c>
       <c r="Y3" t="n">
         <v>93</v>
@@ -1159,17 +1159,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1178,69 +1178,73 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.96</v>
+        <v>8.19999981</v>
       </c>
       <c r="H4" t="n">
-        <v>3.96</v>
+        <v>8.19999981</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>B - %65.7 (n=680); C - %62.2 (n=1250); D - %65.6 (n=218); F - %61.1 (n=1052); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>-0.2518899225298021</v>
+        <v>0.6134992924085703</v>
       </c>
       <c r="K4" t="n">
-        <v>3.125002416992251</v>
+        <v>7.189538598829559</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.246888457161011</v>
+        <v>-4.651169213087892</v>
       </c>
       <c r="M4" t="n">
-        <v>4284</v>
+        <v>6020</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0.5485527544351074</v>
+        <v>0.5463455149501661</v>
       </c>
       <c r="O4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="Q4" t="n">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="U4" t="n">
-        <v>4282</v>
+        <v>6015</v>
       </c>
       <c r="V4" s="4" t="n">
-        <v>0.6529659037832788</v>
+        <v>0.6555278470490441</v>
       </c>
       <c r="W4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="X4" s="4" t="n">
-        <v>0.696969696969697</v>
+        <v>0.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="Z4" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AB4" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1272,24 +1276,24 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.96</v>
+        <v>3.93000007</v>
       </c>
       <c r="H5" t="n">
-        <v>3.96</v>
+        <v>3.93000007</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); K - %61.1 (n=1312)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>-0.2518899225298021</v>
+        <v>-1.007555659892523</v>
       </c>
       <c r="K5" t="n">
-        <v>3.125002416992251</v>
+        <v>2.343754221598404</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.246888457161011</v>
+        <v>-1.995016344425493</v>
       </c>
       <c r="M5" t="n">
         <v>6020</v>
@@ -1307,7 +1311,7 @@
         <v>161</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1331,7 +1335,7 @@
         <v>159</v>
       </c>
       <c r="Z5" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA5" t="n">
         <v>3</v>
@@ -1351,17 +1355,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bearish Engulfing</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1370,72 +1374,72 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.85</v>
+        <v>134.19999695</v>
       </c>
       <c r="H6" t="n">
-        <v>2.85</v>
+        <v>134.19999695</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); K - %61.1 (n=1312)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-4.999999999999993</v>
+        <v>-1.323531654411758</v>
       </c>
       <c r="K6" t="n">
-        <v>7.954541365358292</v>
+        <v>2.130900441388839</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3496468653722662</v>
+        <v>0.298949096324419</v>
       </c>
       <c r="M6" t="n">
-        <v>5100</v>
+        <v>6020</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.5905882352941176</v>
+        <v>0.5463455149501661</v>
       </c>
       <c r="O6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.6338028169014085</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>5091</v>
+        <v>6015</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.6870948733058339</v>
+        <v>0.6555278470490441</v>
       </c>
       <c r="W6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.6935483870967742</v>
+        <v>0.5735294117647058</v>
       </c>
       <c r="Y6" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1449,17 +1453,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Bearish Engulfing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1468,69 +1472,73 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>442</v>
+        <v>2.83999991</v>
       </c>
       <c r="H7" t="n">
-        <v>442</v>
+        <v>2.83999991</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); F - %61.1 (n=1052); G - %60.9 (n=470); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
+          <t>B - %65.7 (n=680); C - %62.2 (n=1250); E - %61.2 (n=1308); K - %61.1 (n=1312)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3.512880562060894</v>
+        <v>-5.333336333333339</v>
       </c>
       <c r="K7" t="n">
-        <v>3.573520796719398</v>
+        <v>7.575750091827649</v>
       </c>
       <c r="L7" t="n">
-        <v>1.843317972350222</v>
+        <v>-0.6993003741014192</v>
       </c>
       <c r="M7" t="n">
-        <v>4284</v>
+        <v>5100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.5485527544351074</v>
+        <v>0.5905882352941176</v>
       </c>
       <c r="O7" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>142</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6338028169014085</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U7" t="n">
-        <v>4282</v>
+        <v>5091</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.6529659037832788</v>
+        <v>0.6870948733058339</v>
       </c>
       <c r="W7" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.6744186046511628</v>
+        <v>0.6935483870967742</v>
       </c>
       <c r="Y7" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.746268656716418</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1543,7 +1551,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1562,24 +1570,24 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.33</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
-        <v>1.33</v>
+        <v>36</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); D - %65.6 (n=218); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>B - %65.7 (n=680); C - %62.2 (n=1250); E - %61.2 (n=1308); F - %61.1 (n=1052); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>-3.007518700748335e-06</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="K8" t="n">
-        <v>2.307696242603718</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.919708029197088</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="M8" t="n">
         <v>5100</v>
@@ -1588,10 +1596,10 @@
         <v>0.5905882352941176</v>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="Q8" t="n">
         <v>142</v>
@@ -1600,9 +1608,11 @@
         <v>0.6338028169014085</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U8" t="n">
         <v>5091</v>
       </c>
@@ -1610,10 +1620,10 @@
         <v>0.6870948733058339</v>
       </c>
       <c r="W8" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="Y8" t="n">
         <v>134</v>
@@ -1622,9 +1632,11 @@
         <v>0.746268656716418</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AB8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1637,17 +1649,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Evening Star</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1656,64 +1668,64 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>108.5</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>108.5</v>
+        <v>36</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>B - %65.7 (n=680); C - %62.2 (n=1250); E - %61.2 (n=1308); F - %61.1 (n=1052); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>-1.093889684014249</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="K9" t="n">
-        <v>3.136885119462929</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1846693853809533</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="M9" t="n">
-        <v>4284</v>
+        <v>783</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.5485527544351074</v>
+        <v>0.5977011494252874</v>
       </c>
       <c r="O9" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="4" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>4282</v>
+        <v>783</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.6529659037832788</v>
+        <v>0.6922094508301405</v>
       </c>
       <c r="W9" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y9" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.8</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1750,10 +1762,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>412</v>
+        <v>413.5</v>
       </c>
       <c r="H10" t="n">
-        <v>412</v>
+        <v>413.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1761,13 +1773,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>4.435994930291498</v>
+        <v>4.816223067173642</v>
       </c>
       <c r="K10" t="n">
-        <v>6.048906048906044</v>
+        <v>6.43500643500643</v>
       </c>
       <c r="L10" t="n">
-        <v>4.040404040404044</v>
+        <v>4.419191919191912</v>
       </c>
       <c r="M10" t="n">
         <v>5100</v>
@@ -1825,7 +1837,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1844,24 +1856,24 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6.16</v>
+        <v>25.86000061</v>
       </c>
       <c r="H11" t="n">
-        <v>6.16</v>
+        <v>25.86000061</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
+          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>-1.282047643408801</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="K11" t="n">
-        <v>1.315790806786721</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.597447704886112</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="M11" t="n">
         <v>4284</v>
@@ -1870,10 +1882,10 @@
         <v>0.5485527544351074</v>
       </c>
       <c r="O11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="Q11" t="n">
         <v>93</v>
@@ -1882,9 +1894,11 @@
         <v>0.5483870967741935</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="U11" t="n">
         <v>4282</v>
       </c>
@@ -1892,10 +1906,10 @@
         <v>0.6529659037832788</v>
       </c>
       <c r="W11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="Y11" t="n">
         <v>93</v>
@@ -1904,9 +1918,11 @@
         <v>0.7096774193548387</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AB11" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1938,24 +1954,24 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>26.06</v>
+        <v>25.86000061</v>
       </c>
       <c r="H12" t="n">
-        <v>26.06</v>
+        <v>25.86000061</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); F - %61.1 (n=1052); G - %60.9 (n=470); K - %61.1 (n=1312); L - %61.4 (n=1010)</t>
+          <t>C - %62.2 (n=1250); E - %61.2 (n=1308); G - %60.9 (n=470); K - %61.1 (n=1312)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.2307692307692344</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.511712373045182</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="L12" t="n">
-        <v>16.96588506703496</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="M12" t="n">
         <v>6020</v>
@@ -1973,7 +1989,7 @@
         <v>161</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S12" t="n">
         <v>2</v>
@@ -1997,7 +2013,7 @@
         <v>159</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA12" t="n">
         <v>2</v>
@@ -2036,10 +2052,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.48</v>
+        <v>2.47000003</v>
       </c>
       <c r="H13" t="n">
-        <v>2.48</v>
+        <v>2.47000003</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -2047,13 +2063,13 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3.333329027777943</v>
+        <v>2.916663628472338</v>
       </c>
       <c r="K13" t="n">
-        <v>5.531919384337014</v>
+        <v>5.106388727931455</v>
       </c>
       <c r="L13" t="n">
-        <v>7.359310147860865</v>
+        <v>6.926411002417598</v>
       </c>
       <c r="M13" t="n">
         <v>5100</v>
@@ -2261,13 +2277,13 @@
         <v>161</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>6015</v>
@@ -2285,7 +2301,7 @@
         <v>159</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA15" t="n">
         <v>1</v>
@@ -2457,7 +2473,7 @@
         <v>161</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -2481,7 +2497,7 @@
         <v>159</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
@@ -3533,7 +3549,7 @@
         <v>161</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3557,7 +3573,7 @@
         <v>159</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA28" t="n">
         <v>1</v>
@@ -3729,7 +3745,7 @@
         <v>161</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S30" t="n">
         <v>2</v>
@@ -3753,7 +3769,7 @@
         <v>159</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA30" t="n">
         <v>2</v>
@@ -3827,7 +3843,7 @@
         <v>161</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3851,7 +3867,7 @@
         <v>159</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA31" t="n">
         <v>3</v>
@@ -3925,7 +3941,7 @@
         <v>161</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -3949,7 +3965,7 @@
         <v>159</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
@@ -4023,7 +4039,7 @@
         <v>161</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4047,13 +4063,13 @@
         <v>159</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA33" t="n">
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -4219,7 +4235,7 @@
         <v>161</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4243,7 +4259,7 @@
         <v>159</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
@@ -4317,7 +4333,7 @@
         <v>161</v>
       </c>
       <c r="R36" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4341,7 +4357,7 @@
         <v>159</v>
       </c>
       <c r="Z36" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA36" t="n">
         <v>3</v>
@@ -4709,7 +4725,7 @@
         <v>161</v>
       </c>
       <c r="R40" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S40" t="n">
         <v>7</v>
@@ -4733,7 +4749,7 @@
         <v>159</v>
       </c>
       <c r="Z40" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA40" t="n">
         <v>7</v>
@@ -4807,7 +4823,7 @@
         <v>161</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S41" t="n">
         <v>2</v>
@@ -4831,7 +4847,7 @@
         <v>159</v>
       </c>
       <c r="Z41" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA41" t="n">
         <v>2</v>
@@ -4905,7 +4921,7 @@
         <v>161</v>
       </c>
       <c r="R42" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4929,7 +4945,7 @@
         <v>159</v>
       </c>
       <c r="Z42" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA42" t="n">
         <v>3</v>
@@ -5101,7 +5117,7 @@
         <v>161</v>
       </c>
       <c r="R44" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5125,7 +5141,7 @@
         <v>159</v>
       </c>
       <c r="Z44" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA44" t="n">
         <v>1</v>
@@ -5199,7 +5215,7 @@
         <v>161</v>
       </c>
       <c r="R45" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5223,7 +5239,7 @@
         <v>159</v>
       </c>
       <c r="Z45" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA45" t="n">
         <v>2</v>
@@ -5395,7 +5411,7 @@
         <v>161</v>
       </c>
       <c r="R47" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5419,7 +5435,7 @@
         <v>159</v>
       </c>
       <c r="Z47" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA47" t="n">
         <v>3</v>
@@ -5591,7 +5607,7 @@
         <v>161</v>
       </c>
       <c r="R49" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -5615,7 +5631,7 @@
         <v>159</v>
       </c>
       <c r="Z49" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA49" t="n">
         <v>1</v>
@@ -5885,7 +5901,7 @@
         <v>161</v>
       </c>
       <c r="R52" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5909,7 +5925,7 @@
         <v>159</v>
       </c>
       <c r="Z52" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA52" t="n">
         <v>5</v>
@@ -5983,7 +5999,7 @@
         <v>161</v>
       </c>
       <c r="R53" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S53" t="n">
         <v>2</v>
@@ -6007,7 +6023,7 @@
         <v>159</v>
       </c>
       <c r="Z53" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA53" t="n">
         <v>2</v>
@@ -6375,7 +6391,7 @@
         <v>161</v>
       </c>
       <c r="R57" s="4" t="n">
-        <v>0.6521739130434783</v>
+        <v>0.6583850931677019</v>
       </c>
       <c r="S57" t="n">
         <v>7</v>
@@ -6399,7 +6415,7 @@
         <v>159</v>
       </c>
       <c r="Z57" s="4" t="n">
-        <v>0.7672955974842768</v>
+        <v>0.7735849056603774</v>
       </c>
       <c r="AA57" t="n">
         <v>7</v>
@@ -7957,80 +7973,80 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Piercing Line</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>11.36</v>
+        <v>294</v>
       </c>
       <c r="H2" t="n">
-        <v>4282</v>
+        <v>649</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.4465203176085941</v>
+        <v>0.5701078582434514</v>
       </c>
       <c r="J2" t="n">
-        <v>2348</v>
+        <v>430</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.717206132879046</v>
+        <v>0.7813953488372093</v>
       </c>
       <c r="L2" t="n">
-        <v>2796</v>
+        <v>493</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.6838340486409156</v>
+        <v>0.7505070993914807</v>
       </c>
       <c r="N2" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.3269230769230769</v>
+        <v>0.75</v>
       </c>
       <c r="P2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6296296296296297</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.5268817204301075</v>
+        <v>0.5</v>
       </c>
       <c r="V2" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="W2" s="4" t="n">
         <v>0.8235294117647058</v>
       </c>
       <c r="X2" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="Y2" s="4" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -8056,7 +8072,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -8075,7 +8091,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>704</v>
+        <v>3.91000009</v>
       </c>
       <c r="H3" t="n">
         <v>4282</v>
@@ -8096,22 +8112,22 @@
         <v>0.6838340486409156</v>
       </c>
       <c r="N3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.35</v>
       </c>
       <c r="P3" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="T3" t="n">
         <v>93</v>
@@ -8157,17 +8173,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -8176,74 +8192,80 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.96</v>
+        <v>8.19999981</v>
       </c>
       <c r="H4" t="n">
-        <v>4282</v>
+        <v>6015</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.4465203176085941</v>
+        <v>0.4483790523690773</v>
       </c>
       <c r="J4" t="n">
-        <v>2348</v>
+        <v>3284</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.717206132879046</v>
+        <v>0.7274665042630938</v>
       </c>
       <c r="L4" t="n">
-        <v>2796</v>
+        <v>3943</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.6838340486409156</v>
+        <v>0.6839969566320061</v>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="P4" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="R4" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="T4" t="n">
-        <v>93</v>
+        <v>159</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.5268817204301075</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V4" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="X4" t="n">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="AA4" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE4" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8275,7 +8297,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>3.96</v>
+        <v>3.93000007</v>
       </c>
       <c r="H5" t="n">
         <v>6015</v>
@@ -8317,7 +8339,7 @@
         <v>159</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>0.6352201257861635</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V5" t="n">
         <v>105</v>
@@ -8326,10 +8348,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="X5" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y5" s="4" t="n">
-        <v>0.8278688524590164</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z5" t="n">
         <v>3</v>
@@ -8361,17 +8383,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bearish Engulfing</t>
+          <t>Shooting Star</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -8380,80 +8402,76 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.85</v>
+        <v>134.19999695</v>
       </c>
       <c r="H6" t="n">
-        <v>5091</v>
+        <v>6015</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.4892948340208211</v>
+        <v>0.4483790523690773</v>
       </c>
       <c r="J6" t="n">
-        <v>3005</v>
+        <v>3284</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.7504159733777038</v>
+        <v>0.7274665042630938</v>
       </c>
       <c r="L6" t="n">
-        <v>3498</v>
+        <v>3943</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.7121212121212122</v>
+        <v>0.6839969566320061</v>
       </c>
       <c r="N6" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.532258064516129</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="P6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="R6" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.7674418604651163</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="T6" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.5895522388059702</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V6" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.8390804597701149</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="X6" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.79</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AC6" s="4" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE6" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8466,17 +8484,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Bearish Engulfing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -8485,74 +8503,80 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>442</v>
+        <v>2.83999991</v>
       </c>
       <c r="H7" t="n">
-        <v>4282</v>
+        <v>5091</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.4465203176085941</v>
+        <v>0.4892948340208211</v>
       </c>
       <c r="J7" t="n">
-        <v>2348</v>
+        <v>3005</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.717206132879046</v>
+        <v>0.7504159733777038</v>
       </c>
       <c r="L7" t="n">
-        <v>2796</v>
+        <v>3498</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.6838340486409156</v>
+        <v>0.7121212121212122</v>
       </c>
       <c r="N7" t="n">
+        <v>62</v>
+      </c>
+      <c r="O7" s="4" t="n">
+        <v>0.532258064516129</v>
+      </c>
+      <c r="P7" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="R7" t="n">
         <v>43</v>
       </c>
-      <c r="O7" s="4" t="n">
-        <v>0.4651162790697674</v>
-      </c>
-      <c r="P7" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q7" s="4" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="R7" t="n">
-        <v>29</v>
-      </c>
       <c r="S7" s="4" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="T7" t="n">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.5268817204301075</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="V7" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8390804597701149</v>
       </c>
       <c r="X7" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AE7" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8565,7 +8589,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8584,7 +8608,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.33</v>
+        <v>36</v>
       </c>
       <c r="H8" t="n">
         <v>5091</v>
@@ -8605,22 +8629,22 @@
         <v>0.7121212121212122</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="T8" t="n">
         <v>134</v>
@@ -8641,17 +8665,23 @@
         <v>0.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AE8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8664,17 +8694,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Doji</t>
+          <t>Evening Star</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -8683,61 +8713,59 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>108.5</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>4282</v>
+        <v>783</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.4465203176085941</v>
+        <v>0.491698595146871</v>
       </c>
       <c r="J9" t="n">
-        <v>2348</v>
+        <v>468</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.717206132879046</v>
+        <v>0.7414529914529915</v>
       </c>
       <c r="L9" t="n">
-        <v>2796</v>
+        <v>542</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6838340486409156</v>
+        <v>0.7103321033210332</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.4714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P9" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q9" s="4" t="n">
-        <v>0.775</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.5268817204301075</v>
+        <v>0.7</v>
       </c>
       <c r="V9" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="X9" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.7424242424242424</v>
+        <v>0.875</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
@@ -8782,7 +8810,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>412</v>
+        <v>413.5</v>
       </c>
       <c r="H10" t="n">
         <v>5091</v>
@@ -8862,7 +8890,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8881,7 +8909,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6.16</v>
+        <v>25.86000061</v>
       </c>
       <c r="H11" t="n">
         <v>4282</v>
@@ -8902,22 +8930,22 @@
         <v>0.6838340486409156</v>
       </c>
       <c r="N11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.5166666666666667</v>
       </c>
       <c r="P11" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="R11" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="T11" t="n">
         <v>93</v>
@@ -8938,17 +8966,23 @@
         <v>0.7424242424242424</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AE11" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8980,7 +9014,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>26.06</v>
+        <v>25.86000061</v>
       </c>
       <c r="H12" t="n">
         <v>6015</v>
@@ -9022,7 +9056,7 @@
         <v>159</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.6352201257861635</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V12" t="n">
         <v>105</v>
@@ -9031,10 +9065,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="X12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.8278688524590164</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z12" t="n">
         <v>2</v>
@@ -9085,7 +9119,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.48</v>
+        <v>2.47000003</v>
       </c>
       <c r="H13" t="n">
         <v>5091</v>
@@ -9325,7 +9359,7 @@
         <v>159</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.6352201257861635</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V15" t="n">
         <v>105</v>
@@ -9334,10 +9368,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="X15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.8278688524590164</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z15" t="n">
         <v>1</v>
@@ -9535,7 +9569,7 @@
         <v>159</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.6352201257861635</v>
+        <v>0.6415094339622641</v>
       </c>
       <c r="V17" t="n">
         <v>105</v>
@@ -9544,10 +9578,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="X17" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.8278688524590164</v>
+        <v>0.8292682926829268</v>
       </c>
       <c r="Z17" t="n">
         <v>1</v>
@@ -10620,7 +10654,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="47" customWidth="1" min="11" max="11"/>
@@ -10778,17 +10812,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10798,52 +10832,52 @@
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.645023262982315</v>
+        <v>-2.244389027431426</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>621</v>
+        <v>167</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.499194847020934</v>
+        <v>0.688622754491018</v>
       </c>
       <c r="L2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.2</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" s="4" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>620</v>
+        <v>167</v>
       </c>
       <c r="S2" s="4" t="n">
-        <v>0.6274193548387097</v>
+        <v>0.8143712574850299</v>
       </c>
       <c r="T2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W2" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -10861,17 +10895,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10881,7 +10915,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.645023262982315</v>
+        <v>-2.244389027431426</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -10889,41 +10923,41 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>835</v>
+        <v>378</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.5053892215568863</v>
+        <v>0.6693121693121693</v>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" s="4" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>834</v>
+        <v>378</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>0.6306954436450839</v>
+        <v>0.7751322751322751</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W3" s="4" t="n">
         <v>0.6666666666666666</v>
@@ -10944,17 +10978,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10964,7 +10998,7 @@
         <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.645023262982315</v>
+        <v>-2.244389027431426</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -10972,44 +11006,44 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>918</v>
+        <v>447</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0.5130718954248366</v>
+        <v>0.6756152125279642</v>
       </c>
       <c r="L4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>0.4615384615384616</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="4" t="inlineStr"/>
       <c r="R4" t="n">
-        <v>917</v>
+        <v>447</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>0.6357688113413305</v>
+        <v>0.7740492170022372</v>
       </c>
       <c r="T4" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="U4" s="4" t="n">
-        <v>0.4615384615384616</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W4" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -11027,17 +11061,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -11047,52 +11081,48 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>5.674418604651166</v>
+        <v>-0.3389830508474523</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[4,6)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>814</v>
+        <v>123</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.5110565110565111</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="4" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>814</v>
+        <v>123</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>0.6265356265356266</v>
+        <v>0.6991869918699187</v>
       </c>
       <c r="T5" t="n">
-        <v>10</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U5" s="4" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="W5" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -11110,17 +11140,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -11130,52 +11160,52 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.674418604651166</v>
+        <v>-0.3389830508474523</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[4,8)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1331</v>
+        <v>274</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.5507137490608565</v>
+        <v>0.6386861313868614</v>
       </c>
       <c r="L6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N6" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="4" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1331</v>
+        <v>274</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.6528925619834711</v>
+        <v>0.7481751824817519</v>
       </c>
       <c r="T6" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V6" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -11193,17 +11223,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -11213,52 +11243,52 @@
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.674418604651166</v>
+        <v>-0.3389830508474523</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2394</v>
+        <v>399</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.6365914786967418</v>
       </c>
       <c r="L7" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.4411764705882353</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.46</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="4" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>2392</v>
+        <v>399</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.6212374581939799</v>
+        <v>0.7443609022556391</v>
       </c>
       <c r="T7" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V7" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.66</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -11276,17 +11306,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -11296,53 +11326,49 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>3.085295152519429</v>
+        <v>-15.81961345740873</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[-16,-14)</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>497</v>
+        <v>33</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.4728370221327968</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" s="4" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>497</v>
+        <v>33</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.5855130784708249</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>16</v>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>0.625</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
       <c r="X8" t="n">
         <v>0</v>
       </c>
@@ -11359,17 +11385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -11379,52 +11405,52 @@
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.085295152519429</v>
+        <v>-15.81961345740873</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-16,-12)</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>909</v>
+        <v>68</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.4741474147414741</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.3870967741935484</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="inlineStr"/>
       <c r="R9" t="n">
-        <v>909</v>
+        <v>68</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.6028602860286029</v>
+        <v>0.8088235294117647</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.6774193548387096</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -11442,17 +11468,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AKSA</t>
+          <t>ASTOR</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>PIERCING_LINE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SHORT</t>
+          <t>LONG</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -11462,52 +11488,52 @@
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.085295152519429</v>
+        <v>-15.81961345740873</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-18,-12)</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1432</v>
+        <v>78</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.4930167597765363</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="L10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.4473684210526316</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1430</v>
+        <v>78</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.6132867132867132</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.3888888888888889</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -11525,7 +11551,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -11545,52 +11571,52 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.363074811256006</v>
+        <v>5.107528453433918</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[4,6)</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>214</v>
+        <v>575</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.5233644859813084</v>
+        <v>0.5826086956521739</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>214</v>
+        <v>575</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.6401869158878505</v>
+        <v>0.6747826086956522</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -11608,7 +11634,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11628,52 +11654,52 @@
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.363074811256006</v>
+        <v>5.107528453433918</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>835</v>
+        <v>880</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.5053892215568863</v>
+        <v>0.5806818181818182</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="4" t="inlineStr"/>
       <c r="R12" t="n">
-        <v>834</v>
+        <v>880</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.6306954436450839</v>
+        <v>0.6693181818181818</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -11691,7 +11717,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11711,57 +11737,61 @@
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.363074811256006</v>
+        <v>5.107528453433918</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>918</v>
+        <v>2515</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.5130718954248366</v>
+        <v>0.5244532803180915</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.59375</v>
       </c>
       <c r="N13" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R13" t="n">
-        <v>917</v>
+        <v>2514</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.6357688113413305</v>
+        <v>0.6356404136833731</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6875</v>
       </c>
       <c r="V13" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -11774,7 +11804,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11794,52 +11824,52 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.607267645003496</v>
+        <v>2.356025174063303</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>202</v>
+        <v>929</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5693069306930693</v>
+        <v>0.5048439181916039</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="N14" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="4" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>202</v>
+        <v>929</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6732673267326733</v>
+        <v>0.635091496232508</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V14" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -11857,7 +11887,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11877,57 +11907,61 @@
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.607267645003496</v>
+        <v>2.356025174063303</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>273</v>
+        <v>1580</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.5787545787545788</v>
+        <v>0.4962025316455696</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R15" t="n">
-        <v>273</v>
+        <v>1578</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.6776556776556777</v>
+        <v>0.6185044359949303</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V15" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11940,7 +11974,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11960,57 +11994,61 @@
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.607267645003496</v>
+        <v>2.356025174063303</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>320</v>
+        <v>2394</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.578125</v>
+        <v>0.5012531328320802</v>
       </c>
       <c r="L16" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1</v>
+        <v>0.3928571428571428</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.46</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R16" t="n">
-        <v>320</v>
+        <v>2392</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.68125</v>
+        <v>0.6212374581939799</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.66</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -12023,7 +12061,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -12043,61 +12081,49 @@
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.097040605643497</v>
+        <v>-13.87664924120396</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[-14,-12)</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.5034965034965035</v>
+        <v>0.7</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr"/>
       <c r="N17" t="n">
-        <v>9</v>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="4" t="inlineStr"/>
       <c r="R17" t="n">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6643356643356644</v>
+        <v>0.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U17" s="4" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W17" s="4" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -12110,7 +12136,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -12130,61 +12156,49 @@
         <v>4</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.097040605643497</v>
+        <v>-13.87664924120396</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-16,-12)</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>403</v>
+        <v>14</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.4689826302729528</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>0.2857142857142857</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M18" s="4" t="inlineStr"/>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
+      <c r="R18" t="n">
         <v>14</v>
       </c>
-      <c r="O18" s="4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>403</v>
-      </c>
       <c r="S18" s="4" t="n">
-        <v>0.5955334987593052</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="T18" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>0.2857142857142857</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U18" s="4" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>14</v>
-      </c>
-      <c r="W18" s="4" t="n">
-        <v>0.6428571428571429</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W18" s="4" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -12197,7 +12211,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BRSAN</t>
+          <t>BTCIM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12217,61 +12231,49 @@
         <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.097040605643497</v>
+        <v>-13.87664924120396</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[-18,-12)</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>491</v>
+        <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4887983706720977</v>
+        <v>0.6875</v>
       </c>
       <c r="L19" t="n">
-        <v>9</v>
-      </c>
-      <c r="M19" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>17</v>
-      </c>
-      <c r="O19" s="4" t="n">
-        <v>0.7058823529411765</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
       <c r="R19" t="n">
-        <v>491</v>
+        <v>16</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.6089613034623218</v>
+        <v>0.8125</v>
       </c>
       <c r="T19" t="n">
-        <v>9</v>
-      </c>
-      <c r="U19" s="4" t="n">
-        <v>0.4444444444444444</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U19" s="4" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>17</v>
-      </c>
-      <c r="W19" s="4" t="n">
-        <v>0.7058823529411765</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W19" s="4" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -12284,12 +12286,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -12304,57 +12306,61 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2518899225298021</v>
+        <v>0.6134992924085703</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>621</v>
+        <v>1496</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.499194847020934</v>
+        <v>0.4839572192513369</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="n">
-        <v>620</v>
+        <v>1494</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.6274193548387097</v>
+        <v>0.6097724230254351</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -12367,12 +12373,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -12387,57 +12393,61 @@
         <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2518899225298021</v>
+        <v>0.6134992924085703</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>835</v>
+        <v>2724</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5053892215568863</v>
+        <v>0.5077092511013216</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M21" s="4" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="N21" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>0.5</v>
+      </c>
       <c r="R21" t="n">
-        <v>834</v>
+        <v>2721</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6306954436450839</v>
+        <v>0.6262403528114664</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8125</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Y21" s="4" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12450,12 +12460,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -12470,57 +12480,61 @@
         <v>6</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2518899225298021</v>
+        <v>0.6134992924085703</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>918</v>
+        <v>3523</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5130718954248366</v>
+        <v>0.5288106727221118</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6767676767676768</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="R22" t="n">
-        <v>917</v>
+        <v>3520</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.6357688113413305</v>
+        <v>0.6428977272727273</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.5</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="V22" t="n">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y22" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -12533,12 +12547,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12553,57 +12567,61 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.125002416992251</v>
+        <v>7.189538598829559</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[6,8)</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>929</v>
+        <v>709</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.5048439181916039</v>
+        <v>0.5923836389280677</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.2</v>
+        <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R23" t="n">
-        <v>929</v>
+        <v>709</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.635091496232508</v>
+        <v>0.6812411847672779</v>
       </c>
       <c r="T23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="V23" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y23" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -12616,12 +12634,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -12636,57 +12654,61 @@
         <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.125002416992251</v>
+        <v>7.189538598829559</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1580</v>
+        <v>1811</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4962025316455696</v>
+        <v>0.5461071231363888</v>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N24" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Q24" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="R24" t="n">
-        <v>1578</v>
+        <v>1811</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.6185044359949303</v>
+        <v>0.650469353948095</v>
       </c>
       <c r="T24" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.4</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="V24" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -12699,12 +12721,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12719,57 +12741,61 @@
         <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>3.125002416992251</v>
+        <v>7.189538598829559</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[6,12)</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2394</v>
+        <v>1500</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.6013333333333334</v>
       </c>
       <c r="L25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
       <c r="N25" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.46</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q25" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R25" t="n">
-        <v>2392</v>
+        <v>1500</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>0.6212374581939799</v>
+        <v>0.6926666666666667</v>
       </c>
       <c r="T25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="V25" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.66</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -12782,12 +12808,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12802,25 +12828,23 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.246888457161011</v>
+        <v>-4.651169213087892</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.45</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
       <c r="N26" t="n">
         <v>5</v>
       </c>
@@ -12832,17 +12856,15 @@
       </c>
       <c r="Q26" s="4" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>260</v>
+        <v>124</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" s="4" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U26" s="4" t="inlineStr"/>
       <c r="V26" t="n">
         <v>5</v>
       </c>
@@ -12865,12 +12887,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -12885,52 +12907,52 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.246888457161011</v>
+        <v>-4.651169213087892</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>403</v>
+        <v>205</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.4689826302729528</v>
+        <v>0.551219512195122</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.9</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="4" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>403</v>
+        <v>205</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.5955334987593052</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="T27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.9</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -12948,12 +12970,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EUREN</t>
+          <t>DAPGM</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12968,7 +12990,7 @@
         <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.246888457161011</v>
+        <v>-4.651169213087892</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -12976,44 +12998,44 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>491</v>
+        <v>681</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.4887983706720977</v>
+        <v>0.5051395007342144</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N28" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="4" t="inlineStr"/>
       <c r="R28" t="n">
-        <v>491</v>
+        <v>680</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.6089613034623218</v>
+        <v>0.6323529411764706</v>
       </c>
       <c r="T28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V28" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -13051,7 +13073,7 @@
         <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2518899225298021</v>
+        <v>-1.007555659892523</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13138,7 +13160,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2518899225298021</v>
+        <v>-1.007555659892523</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13225,7 +13247,7 @@
         <v>6</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2518899225298021</v>
+        <v>-1.007555659892523</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13312,7 +13334,7 @@
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>3.125002416992251</v>
+        <v>2.343754221598404</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13399,7 +13421,7 @@
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>3.125002416992251</v>
+        <v>2.343754221598404</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13446,7 +13468,7 @@
         <v>53</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.7169811320754716</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="X33" t="n">
         <v>3</v>
@@ -13486,7 +13508,7 @@
         <v>6</v>
       </c>
       <c r="H34" t="n">
-        <v>3.125002416992251</v>
+        <v>2.343754221598404</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13533,7 +13555,7 @@
         <v>88</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>0.7727272727272727</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="X34" t="n">
         <v>3</v>
@@ -13573,7 +13595,7 @@
         <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.246888457161011</v>
+        <v>-1.995016344425493</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13660,7 +13682,7 @@
         <v>4</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.246888457161011</v>
+        <v>-1.995016344425493</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13683,7 +13705,7 @@
         <v>25</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -13747,7 +13769,7 @@
         <v>6</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.246888457161011</v>
+        <v>-1.995016344425493</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13770,7 +13792,7 @@
         <v>30</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -13814,12 +13836,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -13834,52 +13856,52 @@
         <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>-4.999999999999993</v>
+        <v>-1.323531654411758</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[-6,-4)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>276</v>
+        <v>836</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0.7210144927536232</v>
+        <v>0.4892344497607656</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N38" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="4" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>275</v>
+        <v>834</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>0.7963636363636364</v>
+        <v>0.5983213429256595</v>
       </c>
       <c r="T38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="V38" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="W38" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -13897,12 +13919,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -13917,52 +13939,52 @@
         <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.999999999999993</v>
+        <v>-1.323531654411758</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[-8,-4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>370</v>
+        <v>1181</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0.7243243243243244</v>
+        <v>0.497883149872989</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N39" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.6</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="4" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>368</v>
+        <v>1179</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>0.7880434782608695</v>
+        <v>0.6013570822731128</v>
       </c>
       <c r="T39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="V39" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="W39" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -13980,12 +14002,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -14000,7 +14022,7 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>-4.999999999999993</v>
+        <v>-1.323531654411758</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -14008,44 +14030,44 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2394</v>
+        <v>1314</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0.5989974937343359</v>
+        <v>0.5060882800608828</v>
       </c>
       <c r="L40" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N40" t="n">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>0.6027397260273972</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="4" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>2390</v>
+        <v>1312</v>
       </c>
       <c r="S40" s="4" t="n">
-        <v>0.6899581589958159</v>
+        <v>0.6067073170731707</v>
       </c>
       <c r="T40" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="V40" t="n">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="W40" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -14063,12 +14085,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -14083,52 +14105,52 @@
         <v>2</v>
       </c>
       <c r="H41" t="n">
-        <v>7.954541365358292</v>
+        <v>2.130900441388839</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[6,8)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>374</v>
+        <v>1288</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>0.6336898395721925</v>
+        <v>0.4937888198757764</v>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="4" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>374</v>
+        <v>1288</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>0.6978609625668449</v>
+        <v>0.6281055900621118</v>
       </c>
       <c r="T41" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="W41" s="4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -14146,12 +14168,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -14166,57 +14188,61 @@
         <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>7.954541365358292</v>
+        <v>2.130900441388839</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[4,8)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1029</v>
+        <v>2234</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0.5792031098153547</v>
+        <v>0.4923903312444047</v>
       </c>
       <c r="L42" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="N42" t="n">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q42" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R42" t="n">
-        <v>1029</v>
+        <v>2231</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>0.685131195335277</v>
+        <v>0.6203496190049306</v>
       </c>
       <c r="T42" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="V42" t="n">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="W42" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y42" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -14229,12 +14255,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -14249,57 +14275,61 @@
         <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>7.954541365358292</v>
+        <v>2.130900441388839</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[6,12)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>678</v>
+        <v>3336</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0.6312684365781711</v>
+        <v>0.5002997601918465</v>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>0.7</v>
+        <v>0.4137931034482759</v>
       </c>
       <c r="N43" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q43" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R43" t="n">
-        <v>677</v>
+        <v>3333</v>
       </c>
       <c r="S43" s="4" t="n">
-        <v>0.7031019202363368</v>
+        <v>0.6237623762376238</v>
       </c>
       <c r="T43" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>0.8</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="V43" t="n">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="W43" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.7840909090909091</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y43" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -14312,12 +14342,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -14332,40 +14362,42 @@
         <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.3496468653722662</v>
+        <v>0.298949096324419</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>402</v>
+        <v>579</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0.5746268656716418</v>
+        <v>0.4766839378238342</v>
       </c>
       <c r="L44" t="n">
         <v>6</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>0.6875</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q44" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R44" t="n">
-        <v>402</v>
+        <v>579</v>
       </c>
       <c r="S44" s="4" t="n">
-        <v>0.6616915422885572</v>
+        <v>0.5941278065630398</v>
       </c>
       <c r="T44" t="n">
         <v>6</v>
@@ -14374,15 +14406,17 @@
         <v>0.5</v>
       </c>
       <c r="V44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W44" s="4" t="n">
-        <v>0.6875</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y44" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -14395,12 +14429,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -14415,57 +14449,61 @@
         <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.3496468653722662</v>
+        <v>0.298949096324419</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>659</v>
+        <v>1313</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>0.5872534142640364</v>
+        <v>0.4859101294744859</v>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.6</v>
+        <v>0.375</v>
       </c>
       <c r="N45" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>0.6451612903225806</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q45" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R45" t="n">
-        <v>659</v>
+        <v>1313</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>0.6707132018209409</v>
+        <v>0.6047220106626047</v>
       </c>
       <c r="T45" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="V45" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="W45" s="4" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y45" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -14478,12 +14516,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HEKTS</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BEARISH_ENGULFING</t>
+          <t>SHOOTING_STAR</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -14498,57 +14536,61 @@
         <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.3496468653722662</v>
+        <v>0.298949096324419</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>784</v>
+        <v>2078</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0.5969387755102041</v>
+        <v>0.4990375360923965</v>
       </c>
       <c r="L46" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="N46" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q46" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="R46" t="n">
-        <v>784</v>
+        <v>2075</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.620722891566265</v>
       </c>
       <c r="T46" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="V46" t="n">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="W46" s="4" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6721311475409836</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y46" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -14561,12 +14603,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -14581,52 +14623,52 @@
         <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>3.512880562060894</v>
+        <v>-5.333336333333339</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[-6,-4)</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>888</v>
+        <v>276</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0.5202702702702703</v>
+        <v>0.7210144927536232</v>
       </c>
       <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
         <v>12</v>
       </c>
-      <c r="M47" s="4" t="n">
+      <c r="O47" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="N47" t="n">
-        <v>20</v>
-      </c>
-      <c r="O47" s="4" t="n">
-        <v>0.6</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="4" t="inlineStr"/>
       <c r="R47" t="n">
-        <v>888</v>
+        <v>275</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>0.6554054054054054</v>
+        <v>0.7963636363636364</v>
       </c>
       <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
         <v>12</v>
       </c>
-      <c r="U47" s="4" t="n">
+      <c r="W47" s="4" t="n">
         <v>0.5833333333333334</v>
-      </c>
-      <c r="V47" t="n">
-        <v>20</v>
-      </c>
-      <c r="W47" s="4" t="n">
-        <v>0.65</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -14644,12 +14686,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -14664,52 +14706,52 @@
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>3.512880562060894</v>
+        <v>-5.333336333333339</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-8,-4)</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1940</v>
+        <v>370</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0.5072164948453608</v>
+        <v>0.7243243243243244</v>
       </c>
       <c r="L48" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="4" t="inlineStr"/>
       <c r="R48" t="n">
-        <v>1939</v>
+        <v>368</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>0.6240330067044868</v>
+        <v>0.7880434782608695</v>
       </c>
       <c r="T48" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="U48" s="4" t="n">
-        <v>0.6363636363636364</v>
+        <v>1</v>
       </c>
       <c r="V48" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="W48" s="4" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -14727,12 +14769,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -14747,52 +14789,52 @@
         <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>3.512880562060894</v>
+        <v>-5.333336333333339</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2515</v>
+        <v>2394</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0.5244532803180915</v>
+        <v>0.5989974937343359</v>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N49" t="n">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="4" t="inlineStr"/>
       <c r="R49" t="n">
-        <v>2514</v>
+        <v>2390</v>
       </c>
       <c r="S49" s="4" t="n">
-        <v>0.6356404136833731</v>
+        <v>0.6899581589958159</v>
       </c>
       <c r="T49" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>0.6896551724137931</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="V49" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="W49" s="4" t="n">
-        <v>0.7090909090909091</v>
+        <v>0.75</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -14810,12 +14852,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14830,18 +14872,18 @@
         <v>2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.573520796719398</v>
+        <v>7.575750091827649</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[6,8)</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>929</v>
+        <v>374</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>0.5048439181916039</v>
+        <v>0.6336898395721925</v>
       </c>
       <c r="L50" t="n">
         <v>6</v>
@@ -14850,32 +14892,32 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="N50" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P50" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="4" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>929</v>
+        <v>374</v>
       </c>
       <c r="S50" s="4" t="n">
-        <v>0.635091496232508</v>
+        <v>0.6978609625668449</v>
       </c>
       <c r="T50" t="n">
         <v>6</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="V50" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="W50" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -14893,12 +14935,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -14913,18 +14955,18 @@
         <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>3.573520796719398</v>
+        <v>7.575750091827649</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1580</v>
+        <v>1029</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0.4962025316455696</v>
+        <v>0.5792031098153547</v>
       </c>
       <c r="L51" t="n">
         <v>12</v>
@@ -14933,29 +14975,29 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="N51" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.5625</v>
       </c>
       <c r="P51" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="4" t="inlineStr"/>
       <c r="R51" t="n">
-        <v>1578</v>
+        <v>1029</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>0.6185044359949303</v>
+        <v>0.685131195335277</v>
       </c>
       <c r="T51" t="n">
         <v>12</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="V51" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="W51" s="4" t="n">
         <v>0.5833333333333334</v>
@@ -14976,12 +15018,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -14996,52 +15038,52 @@
         <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>3.573520796719398</v>
+        <v>7.575750091827649</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[6,12)</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>2394</v>
+        <v>678</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.6312684365781711</v>
       </c>
       <c r="L52" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7</v>
       </c>
       <c r="N52" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="4" t="inlineStr"/>
       <c r="R52" t="n">
-        <v>2392</v>
+        <v>677</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>0.6212374581939799</v>
+        <v>0.7031019202363368</v>
       </c>
       <c r="T52" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="U52" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8</v>
       </c>
       <c r="V52" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="W52" s="4" t="n">
-        <v>0.66</v>
+        <v>0.5625</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -15059,12 +15101,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -15079,52 +15121,52 @@
         <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1.843317972350222</v>
+        <v>-0.6993003741014192</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0.4757281553398058</v>
+        <v>0.5746268656716418</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.6875</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="4" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>0.6237864077669902</v>
+        <v>0.6616915422885572</v>
       </c>
       <c r="T53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U53" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V53" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W53" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6875</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -15142,12 +15184,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -15162,52 +15204,52 @@
         <v>4</v>
       </c>
       <c r="H54" t="n">
-        <v>1.843317972350222</v>
+        <v>-0.6993003741014192</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>909</v>
+        <v>659</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0.4741474147414741</v>
+        <v>0.5872534142640364</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="N54" t="n">
         <v>31</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="4" t="inlineStr"/>
       <c r="R54" t="n">
-        <v>909</v>
+        <v>659</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>0.6028602860286029</v>
+        <v>0.6707132018209409</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="V54" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="W54" s="4" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -15225,12 +15267,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MPARK</t>
+          <t>HEKTS</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>BEARISH_ENGULFING</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -15245,52 +15287,52 @@
         <v>6</v>
       </c>
       <c r="H55" t="n">
-        <v>1.843317972350222</v>
+        <v>-0.6993003741014192</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1432</v>
+        <v>784</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0.4930167597765363</v>
+        <v>0.5969387755102041</v>
       </c>
       <c r="L55" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="N55" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="4" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>1430</v>
+        <v>784</v>
       </c>
       <c r="S55" s="4" t="n">
-        <v>0.6132867132867132</v>
+        <v>0.6785714285714286</v>
       </c>
       <c r="T55" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="V55" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="W55" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7419354838709677</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -15308,7 +15350,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -15328,57 +15370,61 @@
         <v>2</v>
       </c>
       <c r="H56" t="n">
-        <v>-3.007518700748335e-06</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1341</v>
+        <v>678</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0.5540641312453393</v>
+        <v>0.5737463126843658</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N56" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="O56" s="4" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.7</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q56" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R56" t="n">
-        <v>1339</v>
+        <v>677</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>0.6460044809559373</v>
+        <v>0.6765140324963073</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U56" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V56" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="W56" s="4" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y56" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -15391,7 +15437,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -15411,57 +15457,61 @@
         <v>4</v>
       </c>
       <c r="H57" t="n">
-        <v>-3.007518700748335e-06</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2118</v>
+        <v>2031</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>0.5830972615675165</v>
+        <v>0.5480059084194978</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N57" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>0.6229508196721312</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q57" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R57" t="n">
-        <v>2115</v>
+        <v>2028</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>0.6761229314420804</v>
+        <v>0.6632149901380671</v>
       </c>
       <c r="T57" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U57" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="W57" s="4" t="n">
-        <v>0.7833333333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y57" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -15474,7 +15524,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -15494,57 +15544,61 @@
         <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>-3.007518700748335e-06</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2394</v>
+        <v>2273</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0.5989974937343359</v>
+        <v>0.5538935327760669</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="N58" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>0.6027397260273972</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q58" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R58" t="n">
-        <v>2390</v>
+        <v>2270</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>0.6899581589958159</v>
+        <v>0.6665198237885462</v>
       </c>
       <c r="T58" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="U58" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V58" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="W58" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y58" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15557,7 +15611,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -15577,52 +15631,52 @@
         <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>2.307696242603718</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[6,8)</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>973</v>
+        <v>374</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0.539568345323741</v>
+        <v>0.6336898395721925</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="O59" s="4" t="n">
-        <v>0.64</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P59" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="4" t="inlineStr"/>
       <c r="R59" t="n">
-        <v>972</v>
+        <v>374</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>0.6563786008230452</v>
+        <v>0.6978609625668449</v>
       </c>
       <c r="T59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U59" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V59" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="W59" s="4" t="n">
-        <v>0.7916666666666666</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -15640,7 +15694,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -15660,57 +15714,61 @@
         <v>4</v>
       </c>
       <c r="H60" t="n">
-        <v>2.307696242603718</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2133</v>
+        <v>1029</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0.5471167369901547</v>
+        <v>0.5792031098153547</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="O60" s="4" t="n">
-        <v>0.6271186440677966</v>
+        <v>0.5625</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q60" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R60" t="n">
-        <v>2131</v>
+        <v>1029</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>0.65415297982168</v>
+        <v>0.685131195335277</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="V60" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="W60" s="4" t="n">
-        <v>0.75</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y60" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15723,7 +15781,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -15743,52 +15801,52 @@
         <v>6</v>
       </c>
       <c r="H61" t="n">
-        <v>2.307696242603718</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[6,12)</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2788</v>
+        <v>678</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0.5473457675753228</v>
+        <v>0.6312684365781711</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M61" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>20</v>
+      </c>
+      <c r="O61" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="N61" t="n">
-        <v>68</v>
-      </c>
-      <c r="O61" s="4" t="n">
-        <v>0.6470588235294118</v>
       </c>
       <c r="P61" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="4" t="inlineStr"/>
       <c r="R61" t="n">
-        <v>2786</v>
+        <v>677</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>0.659727207465901</v>
+        <v>0.7031019202363368</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V61" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="W61" s="4" t="n">
-        <v>0.765625</v>
+        <v>0.5625</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -15806,7 +15864,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -15826,52 +15884,52 @@
         <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>-2.919708029197088</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[-4,-2)</t>
+          <t>[0,2)</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>257</v>
+        <v>591</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0.6070038910505836</v>
+        <v>0.5346869712351946</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="4" t="inlineStr"/>
       <c r="R62" t="n">
-        <v>257</v>
+        <v>590</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>0.6848249027237354</v>
+        <v>0.6576271186440678</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U62" s="4" t="n">
         <v>1</v>
       </c>
       <c r="V62" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="W62" s="4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="X62" t="n">
         <v>0</v>
@@ -15889,7 +15947,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -15909,52 +15967,52 @@
         <v>4</v>
       </c>
       <c r="H63" t="n">
-        <v>-2.919708029197088</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>659</v>
+        <v>1313</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0.5872534142640364</v>
+        <v>0.5346534653465347</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M63" s="4" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="N63" t="n">
+        <v>44</v>
+      </c>
+      <c r="O63" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>31</v>
-      </c>
-      <c r="O63" s="4" t="n">
-        <v>0.6451612903225806</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="4" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>659</v>
+        <v>1307</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>0.6707132018209409</v>
+        <v>0.6602907421576129</v>
       </c>
       <c r="T63" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="U63" s="4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="V63" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="W63" s="4" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -15972,7 +16030,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -15992,52 +16050,52 @@
         <v>6</v>
       </c>
       <c r="H64" t="n">
-        <v>-2.919708029197088</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>784</v>
+        <v>2023</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0.5969387755102041</v>
+        <v>0.5531389026198715</v>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="N64" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="O64" s="4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.5625</v>
       </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="4" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>784</v>
+        <v>2015</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>0.6785714285714286</v>
+        <v>0.6719602977667494</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="V64" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="W64" s="4" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -16055,12 +16113,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -16075,53 +16133,47 @@
         <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.093889684014249</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[2,4)</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0.499194847020934</v>
+        <v>0.6219512195121951</v>
       </c>
       <c r="L65" t="n">
-        <v>6</v>
-      </c>
-      <c r="M65" s="4" t="n">
-        <v>0.3333333333333333</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M65" s="4" t="inlineStr"/>
       <c r="N65" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="4" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="S65" s="4" t="n">
-        <v>0.6274193548387097</v>
+        <v>0.7073170731707317</v>
       </c>
       <c r="T65" t="n">
-        <v>6</v>
-      </c>
-      <c r="U65" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U65" s="4" t="inlineStr"/>
       <c r="V65" t="n">
-        <v>9</v>
-      </c>
-      <c r="W65" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W65" s="4" t="inlineStr"/>
       <c r="X65" t="n">
         <v>0</v>
       </c>
@@ -16138,12 +16190,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -16158,52 +16210,52 @@
         <v>4</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.093889684014249</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[0,4)</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>835</v>
+        <v>407</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0.5053892215568863</v>
+        <v>0.5798525798525799</v>
       </c>
       <c r="L66" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="M66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>12</v>
+      </c>
+      <c r="O66" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="N66" t="n">
-        <v>15</v>
-      </c>
-      <c r="O66" s="4" t="n">
-        <v>0.4666666666666667</v>
       </c>
       <c r="P66" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="4" t="inlineStr"/>
       <c r="R66" t="n">
-        <v>834</v>
+        <v>407</v>
       </c>
       <c r="S66" s="4" t="n">
-        <v>0.6306954436450839</v>
+        <v>0.6781326781326781</v>
       </c>
       <c r="T66" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>1</v>
       </c>
       <c r="V66" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="W66" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -16221,12 +16273,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -16241,52 +16293,52 @@
         <v>6</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.093889684014249</v>
+        <v>3.151857942053238</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[0,6)</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>918</v>
+        <v>428</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0.5130718954248366</v>
+        <v>0.5841121495327103</v>
       </c>
       <c r="L67" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.5555555555555556</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O67" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="P67" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="4" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>917</v>
+        <v>428</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>0.6357688113413305</v>
+        <v>0.6845794392523364</v>
       </c>
       <c r="T67" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="U67" s="4" t="n">
-        <v>0.7222222222222222</v>
+        <v>1</v>
       </c>
       <c r="V67" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="W67" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
@@ -16304,12 +16356,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -16324,53 +16376,45 @@
         <v>2</v>
       </c>
       <c r="H68" t="n">
-        <v>3.136885119462929</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[2,4)</t>
+          <t>[6,8)</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>929</v>
+        <v>48</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0.5048439181916039</v>
+        <v>0.625</v>
       </c>
       <c r="L68" t="n">
-        <v>13</v>
-      </c>
-      <c r="M68" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M68" s="4" t="inlineStr"/>
       <c r="N68" t="n">
-        <v>19</v>
-      </c>
-      <c r="O68" s="4" t="n">
-        <v>0.4210526315789473</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O68" s="4" t="inlineStr"/>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="4" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>929</v>
+        <v>48</v>
       </c>
       <c r="S68" s="4" t="n">
-        <v>0.635091496232508</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T68" t="n">
-        <v>13</v>
-      </c>
-      <c r="U68" s="4" t="n">
-        <v>0.6153846153846154</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U68" s="4" t="inlineStr"/>
       <c r="V68" t="n">
-        <v>19</v>
-      </c>
-      <c r="W68" s="4" t="n">
-        <v>0.5789473684210527</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W68" s="4" t="inlineStr"/>
       <c r="X68" t="n">
         <v>0</v>
       </c>
@@ -16387,12 +16431,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -16407,52 +16451,52 @@
         <v>4</v>
       </c>
       <c r="H69" t="n">
-        <v>3.136885119462929</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[4,8)</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1580</v>
+        <v>136</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0.4962025316455696</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="L69" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>0.5789473684210527</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="O69" s="4" t="n">
-        <v>0.4722222222222222</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="4" t="inlineStr"/>
       <c r="R69" t="n">
-        <v>1578</v>
+        <v>136</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>0.6185044359949303</v>
+        <v>0.6911764705882353</v>
       </c>
       <c r="T69" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="U69" s="4" t="n">
-        <v>0.631578947368421</v>
+        <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="W69" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -16470,12 +16514,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -16490,52 +16534,52 @@
         <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>3.136885119462929</v>
+        <v>6.194685472629247</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[6,12)</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>2394</v>
+        <v>105</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="L70" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.6176470588235294</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="O70" s="4" t="n">
-        <v>0.46</v>
+        <v>1</v>
       </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="4" t="inlineStr"/>
       <c r="R70" t="n">
-        <v>2392</v>
+        <v>105</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>0.6212374581939799</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="T70" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="U70" s="4" t="n">
-        <v>0.6470588235294118</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="W70" s="4" t="n">
-        <v>0.66</v>
+        <v>1</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
@@ -16553,12 +16597,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -16573,7 +16617,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="n">
-        <v>0.1846693853809533</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -16581,44 +16625,40 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>412</v>
+        <v>85</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0.4757281553398058</v>
+        <v>0.5411764705882353</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
-      </c>
-      <c r="M71" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M71" s="4" t="inlineStr"/>
       <c r="N71" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="O71" s="4" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="4" t="inlineStr"/>
       <c r="R71" t="n">
-        <v>412</v>
+        <v>85</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>0.6237864077669902</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="T71" t="n">
-        <v>3</v>
-      </c>
-      <c r="U71" s="4" t="n">
-        <v>0.6666666666666666</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U71" s="4" t="inlineStr"/>
       <c r="V71" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="W71" s="4" t="n">
-        <v>0.7333333333333333</v>
+        <v>1</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -16636,12 +16676,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -16656,7 +16696,7 @@
         <v>4</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1846693853809533</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -16664,44 +16704,44 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>909</v>
+        <v>189</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0.4741474147414741</v>
+        <v>0.5343915343915344</v>
       </c>
       <c r="L72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.8</v>
       </c>
       <c r="P72" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="4" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>909</v>
+        <v>189</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>0.6028602860286029</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="T72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U72" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="V72" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="W72" s="4" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.8</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -16719,12 +16759,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TRENJ</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DOJI</t>
+          <t>EVENING_STAR</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -16739,7 +16779,7 @@
         <v>6</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1846693853809533</v>
+        <v>0.3344451683986671</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -16747,44 +16787,44 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1432</v>
+        <v>290</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0.4930167597765363</v>
+        <v>0.5620689655172414</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="4" t="inlineStr"/>
       <c r="R73" t="n">
-        <v>1430</v>
+        <v>290</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>0.6132867132867132</v>
+        <v>0.6344827586206897</v>
       </c>
       <c r="T73" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U73" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="V73" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="W73" s="4" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X73" t="n">
         <v>0</v>
@@ -16822,7 +16862,7 @@
         <v>2</v>
       </c>
       <c r="H74" t="n">
-        <v>4.435994930291498</v>
+        <v>4.816223067173642</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -16905,7 +16945,7 @@
         <v>4</v>
       </c>
       <c r="H75" t="n">
-        <v>4.435994930291498</v>
+        <v>4.816223067173642</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -16988,7 +17028,7 @@
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>4.435994930291498</v>
+        <v>4.816223067173642</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -17071,7 +17111,7 @@
         <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>6.048906048906044</v>
+        <v>6.43500643500643</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -17154,7 +17194,7 @@
         <v>4</v>
       </c>
       <c r="H78" t="n">
-        <v>6.048906048906044</v>
+        <v>6.43500643500643</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -17237,7 +17277,7 @@
         <v>6</v>
       </c>
       <c r="H79" t="n">
-        <v>6.048906048906044</v>
+        <v>6.43500643500643</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -17320,7 +17360,7 @@
         <v>2</v>
       </c>
       <c r="H80" t="n">
-        <v>4.040404040404044</v>
+        <v>4.419191919191912</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -17403,7 +17443,7 @@
         <v>4</v>
       </c>
       <c r="H81" t="n">
-        <v>4.040404040404044</v>
+        <v>4.419191919191912</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -17486,7 +17526,7 @@
         <v>6</v>
       </c>
       <c r="H82" t="n">
-        <v>4.040404040404044</v>
+        <v>4.419191919191912</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -17549,7 +17589,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -17569,7 +17609,7 @@
         <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>-1.282047643408801</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -17583,10 +17623,10 @@
         <v>0.499194847020934</v>
       </c>
       <c r="L83" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.5</v>
       </c>
       <c r="N83" t="n">
         <v>9</v>
@@ -17605,10 +17645,10 @@
         <v>0.6274193548387097</v>
       </c>
       <c r="T83" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="U83" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="V83" t="n">
         <v>9</v>
@@ -17632,7 +17672,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -17652,7 +17692,7 @@
         <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.282047643408801</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -17666,7 +17706,7 @@
         <v>0.5053892215568863</v>
       </c>
       <c r="L84" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M84" s="4" t="n">
         <v>0.4444444444444444</v>
@@ -17678,9 +17718,11 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q84" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q84" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R84" t="n">
         <v>834</v>
       </c>
@@ -17688,10 +17730,10 @@
         <v>0.6306954436450839</v>
       </c>
       <c r="T84" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="U84" s="4" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="V84" t="n">
         <v>15</v>
@@ -17700,9 +17742,11 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y84" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y84" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -17715,7 +17759,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17735,7 +17779,7 @@
         <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.282047643408801</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -17749,10 +17793,10 @@
         <v>0.5130718954248366</v>
       </c>
       <c r="L85" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>0.4736842105263158</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N85" t="n">
         <v>18</v>
@@ -17761,9 +17805,11 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q85" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q85" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R85" t="n">
         <v>917</v>
       </c>
@@ -17771,10 +17817,10 @@
         <v>0.6357688113413305</v>
       </c>
       <c r="T85" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="U85" s="4" t="n">
-        <v>0.631578947368421</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="V85" t="n">
         <v>18</v>
@@ -17783,9 +17829,11 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y85" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -17798,7 +17846,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17818,53 +17866,45 @@
         <v>2</v>
       </c>
       <c r="H86" t="n">
-        <v>1.315790806786721</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>651</v>
+        <v>71</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>0.4838709677419355</v>
+        <v>0.6056338028169014</v>
       </c>
       <c r="L86" t="n">
-        <v>9</v>
-      </c>
-      <c r="M86" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M86" s="4" t="inlineStr"/>
       <c r="N86" t="n">
-        <v>17</v>
-      </c>
-      <c r="O86" s="4" t="n">
-        <v>0.5294117647058824</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O86" s="4" t="inlineStr"/>
       <c r="P86" t="n">
         <v>0</v>
       </c>
       <c r="Q86" s="4" t="inlineStr"/>
       <c r="R86" t="n">
-        <v>649</v>
+        <v>71</v>
       </c>
       <c r="S86" s="4" t="n">
-        <v>0.5947611710323575</v>
+        <v>0.6901408450704225</v>
       </c>
       <c r="T86" t="n">
-        <v>9</v>
-      </c>
-      <c r="U86" s="4" t="n">
-        <v>0.5555555555555556</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U86" s="4" t="inlineStr"/>
       <c r="V86" t="n">
-        <v>17</v>
-      </c>
-      <c r="W86" s="4" t="n">
-        <v>0.5882352941176471</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W86" s="4" t="inlineStr"/>
       <c r="X86" t="n">
         <v>0</v>
       </c>
@@ -17881,7 +17921,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17901,52 +17941,52 @@
         <v>4</v>
       </c>
       <c r="H87" t="n">
-        <v>1.315790806786721</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>1580</v>
+        <v>273</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0.4962025316455696</v>
+        <v>0.5787545787545788</v>
       </c>
       <c r="L87" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>0.5925925925925926</v>
+        <v>1</v>
       </c>
       <c r="N87" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P87" t="n">
         <v>0</v>
       </c>
       <c r="Q87" s="4" t="inlineStr"/>
       <c r="R87" t="n">
-        <v>1578</v>
+        <v>273</v>
       </c>
       <c r="S87" s="4" t="n">
-        <v>0.6185044359949303</v>
+        <v>0.6776556776556777</v>
       </c>
       <c r="T87" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="U87" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>1</v>
       </c>
       <c r="V87" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="W87" s="4" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X87" t="n">
         <v>0</v>
@@ -17964,7 +18004,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17984,57 +18024,61 @@
         <v>6</v>
       </c>
       <c r="H88" t="n">
-        <v>1.315790806786721</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>2394</v>
+        <v>320</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0.5012531328320802</v>
+        <v>0.578125</v>
       </c>
       <c r="L88" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.5</v>
       </c>
       <c r="N88" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>0.46</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q88" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R88" t="n">
-        <v>2392</v>
+        <v>320</v>
       </c>
       <c r="S88" s="4" t="n">
-        <v>0.6212374581939799</v>
+        <v>0.68125</v>
       </c>
       <c r="T88" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="U88" s="4" t="n">
-        <v>0.7317073170731707</v>
+        <v>0.5</v>
       </c>
       <c r="V88" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="W88" s="4" t="n">
-        <v>0.66</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" s="4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Y88" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18047,7 +18091,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -18067,52 +18111,52 @@
         <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.597447704886112</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[16,18)</t>
         </is>
       </c>
       <c r="J89" t="n">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0.45</v>
+        <v>0.6540880503144654</v>
       </c>
       <c r="L89" t="n">
         <v>4</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
       </c>
       <c r="Q89" s="4" t="inlineStr"/>
       <c r="R89" t="n">
-        <v>260</v>
+        <v>159</v>
       </c>
       <c r="S89" s="4" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.710691823899371</v>
       </c>
       <c r="T89" t="n">
         <v>4</v>
       </c>
       <c r="U89" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="V89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W89" s="4" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -18130,7 +18174,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18150,52 +18194,52 @@
         <v>4</v>
       </c>
       <c r="H90" t="n">
-        <v>-1.597447704886112</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[-4,0)</t>
+          <t>[16,20)</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0.4689826302729528</v>
+        <v>0.6549295774647887</v>
       </c>
       <c r="L90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M90" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4</v>
+      </c>
+      <c r="O90" s="4" t="n">
         <v>0.5</v>
-      </c>
-      <c r="N90" t="n">
-        <v>14</v>
-      </c>
-      <c r="O90" s="4" t="n">
-        <v>0.6428571428571429</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" s="4" t="inlineStr"/>
       <c r="R90" t="n">
-        <v>403</v>
+        <v>284</v>
       </c>
       <c r="S90" s="4" t="n">
-        <v>0.5955334987593052</v>
+        <v>0.7183098591549296</v>
       </c>
       <c r="T90" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U90" s="4" t="n">
-        <v>0.625</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="V90" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="W90" s="4" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5</v>
       </c>
       <c r="X90" t="n">
         <v>0</v>
@@ -18213,7 +18257,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TURSG</t>
+          <t>VESTL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18233,52 +18277,52 @@
         <v>6</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.597447704886112</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[-6,0)</t>
+          <t>[12,18)</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>491</v>
+        <v>570</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0.4887983706720977</v>
+        <v>0.6385964912280702</v>
       </c>
       <c r="L91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M91" s="4" t="n">
-        <v>0.6</v>
+        <v>0.875</v>
       </c>
       <c r="N91" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O91" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.5</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
       </c>
       <c r="Q91" s="4" t="inlineStr"/>
       <c r="R91" t="n">
-        <v>491</v>
+        <v>570</v>
       </c>
       <c r="S91" s="4" t="n">
-        <v>0.6089613034623218</v>
+        <v>0.7140350877192982</v>
       </c>
       <c r="T91" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U91" s="4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="V91" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="W91" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.75</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -18316,52 +18360,52 @@
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>0.2307692307692344</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[0,2)</t>
+          <t>[-2,0)</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>1496</v>
+        <v>836</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0.4839572192513369</v>
+        <v>0.4892344497607656</v>
       </c>
       <c r="L92" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M92" s="4" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N92" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="O92" s="4" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
       </c>
       <c r="Q92" s="4" t="inlineStr"/>
       <c r="R92" t="n">
-        <v>1494</v>
+        <v>834</v>
       </c>
       <c r="S92" s="4" t="n">
-        <v>0.6097724230254351</v>
+        <v>0.5983213429256595</v>
       </c>
       <c r="T92" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U92" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="V92" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="W92" s="4" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="X92" t="n">
         <v>0</v>
@@ -18399,57 +18443,61 @@
         <v>4</v>
       </c>
       <c r="H93" t="n">
-        <v>0.2307692307692344</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[0,4)</t>
+          <t>[-4,0)</t>
         </is>
       </c>
       <c r="J93" t="n">
-        <v>2724</v>
+        <v>1181</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0.5077092511013216</v>
+        <v>0.497883149872989</v>
       </c>
       <c r="L93" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="M93" s="4" t="n">
-        <v>0.58</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N93" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="O93" s="4" t="n">
-        <v>0.7076923076923077</v>
+        <v>0.6</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q93" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R93" t="n">
-        <v>2721</v>
+        <v>1179</v>
       </c>
       <c r="S93" s="4" t="n">
-        <v>0.6262403528114664</v>
+        <v>0.6013570822731128</v>
       </c>
       <c r="T93" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="U93" s="4" t="n">
-        <v>0.7</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="V93" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="W93" s="4" t="n">
-        <v>0.796875</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y93" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Y93" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18482,57 +18530,61 @@
         <v>6</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2307692307692344</v>
+        <v>-0.5384591923076942</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[0,6)</t>
+          <t>[-6,0)</t>
         </is>
       </c>
       <c r="J94" t="n">
-        <v>3523</v>
+        <v>1314</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0.5288106727221118</v>
+        <v>0.5060882800608828</v>
       </c>
       <c r="L94" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="M94" s="4" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="N94" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>0.6767676767676768</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q94" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="R94" t="n">
-        <v>3520</v>
+        <v>1312</v>
       </c>
       <c r="S94" s="4" t="n">
-        <v>0.6428977272727273</v>
+        <v>0.6067073170731707</v>
       </c>
       <c r="T94" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="U94" s="4" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="V94" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="W94" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Y94" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18565,52 +18617,52 @@
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>-1.511712373045182</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[-2,0)</t>
+          <t>[-4,-2)</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>328</v>
+        <v>132</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0.5670731707317073</v>
+        <v>0.4772727272727273</v>
       </c>
       <c r="L95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M95" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="N95" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O95" s="4" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" s="4" t="inlineStr"/>
       <c r="R95" t="n">
-        <v>328</v>
+        <v>130</v>
       </c>
       <c r="S95" s="4" t="n">
-        <v>0.6646341463414634</v>
+        <v>0.5538461538461539</v>
       </c>
       <c r="T95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U95" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="V95" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="W95" s="4" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
@@ -18648,7 +18700,7 @@
         <v>4</v>
       </c>
       <c r="H96" t="n">
-        <v>-1.511712373045182</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -18731,7 +18783,7 @@
         <v>6</v>
       </c>
       <c r="H97" t="n">
-        <v>-1.511712373045182</v>
+        <v>-2.267567992674324</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -18818,7 +18870,7 @@
         <v>2</v>
       </c>
       <c r="H98" t="n">
-        <v>16.96588506703496</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -18901,7 +18953,7 @@
         <v>4</v>
       </c>
       <c r="H99" t="n">
-        <v>16.96588506703496</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -18984,7 +19036,7 @@
         <v>6</v>
       </c>
       <c r="H100" t="n">
-        <v>16.96588506703496</v>
+        <v>16.06822176449403</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -19067,7 +19119,7 @@
         <v>2</v>
       </c>
       <c r="H101" t="n">
-        <v>3.333329027777943</v>
+        <v>2.916663628472338</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -19150,7 +19202,7 @@
         <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>3.333329027777943</v>
+        <v>2.916663628472338</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -19233,7 +19285,7 @@
         <v>6</v>
       </c>
       <c r="H103" t="n">
-        <v>3.333329027777943</v>
+        <v>2.916663628472338</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -19316,7 +19368,7 @@
         <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>5.531919384337014</v>
+        <v>5.106388727931455</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -19399,7 +19451,7 @@
         <v>4</v>
       </c>
       <c r="H105" t="n">
-        <v>5.531919384337014</v>
+        <v>5.106388727931455</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -19482,7 +19534,7 @@
         <v>6</v>
       </c>
       <c r="H106" t="n">
-        <v>5.531919384337014</v>
+        <v>5.106388727931455</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -19565,7 +19617,7 @@
         <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>7.359310147860865</v>
+        <v>6.926411002417598</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -19648,7 +19700,7 @@
         <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>7.359310147860865</v>
+        <v>6.926411002417598</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -19731,7 +19783,7 @@
         <v>6</v>
       </c>
       <c r="H109" t="n">
-        <v>7.359310147860865</v>
+        <v>6.926411002417598</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -20598,13 +20650,13 @@
         <v>7</v>
       </c>
       <c r="O119" s="4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P119" t="n">
         <v>1</v>
       </c>
       <c r="Q119" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R119" t="n">
         <v>241</v>
@@ -20683,13 +20735,13 @@
         <v>9</v>
       </c>
       <c r="O120" s="4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="P120" t="n">
         <v>1</v>
       </c>
       <c r="Q120" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R120" t="n">
         <v>380</v>
@@ -20768,13 +20820,13 @@
         <v>15</v>
       </c>
       <c r="O121" s="4" t="n">
-        <v>0.4</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="P121" t="n">
         <v>1</v>
       </c>
       <c r="Q121" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
         <v>838</v>
@@ -20853,13 +20905,13 @@
         <v>24</v>
       </c>
       <c r="O122" s="4" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="P122" t="n">
         <v>1</v>
       </c>
       <c r="Q122" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" t="n">
         <v>709</v>
@@ -20938,13 +20990,13 @@
         <v>59</v>
       </c>
       <c r="O123" s="4" t="n">
-        <v>0.6271186440677966</v>
+        <v>0.6440677966101694</v>
       </c>
       <c r="P123" t="n">
         <v>1</v>
       </c>
       <c r="Q123" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" t="n">
         <v>1811</v>
@@ -21023,13 +21075,13 @@
         <v>39</v>
       </c>
       <c r="O124" s="4" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="P124" t="n">
         <v>2</v>
       </c>
       <c r="Q124" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R124" t="n">
         <v>1500</v>
@@ -21110,13 +21162,13 @@
         <v>7</v>
       </c>
       <c r="O125" s="4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="P125" t="n">
         <v>1</v>
       </c>
       <c r="Q125" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R125" t="n">
         <v>202</v>
@@ -21195,13 +21247,13 @@
         <v>25</v>
       </c>
       <c r="O126" s="4" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="P126" t="n">
         <v>1</v>
       </c>
       <c r="Q126" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
         <v>556</v>
@@ -21280,13 +21332,13 @@
         <v>30</v>
       </c>
       <c r="O127" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P127" t="n">
         <v>1</v>
       </c>
       <c r="Q127" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
         <v>680</v>
@@ -22223,7 +22275,7 @@
         <v>64</v>
       </c>
       <c r="W138" s="4" t="n">
-        <v>0.796875</v>
+        <v>0.8125</v>
       </c>
       <c r="X138" t="n">
         <v>0</v>
@@ -22308,7 +22360,7 @@
         <v>98</v>
       </c>
       <c r="W139" s="4" t="n">
-        <v>0.7857142857142857</v>
+        <v>0.7959183673469388</v>
       </c>
       <c r="X139" t="n">
         <v>1</v>
@@ -22541,7 +22593,7 @@
         <v>39</v>
       </c>
       <c r="O142" s="4" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="P142" t="n">
         <v>1</v>
@@ -22705,7 +22757,7 @@
         <v>25</v>
       </c>
       <c r="O144" s="4" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="P144" t="n">
         <v>1</v>
@@ -22786,7 +22838,7 @@
         <v>30</v>
       </c>
       <c r="O145" s="4" t="n">
-        <v>0.7</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P145" t="n">
         <v>1</v>
